--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/pre LAM_HRM-2031-0400/Panel 7/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/pre LAM_HRM-2031-0400/Panel 7/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.68732</v>
+        <v>16.78038</v>
       </c>
       <c r="D2" t="n">
-        <v>16.42066</v>
+        <v>16.19695</v>
       </c>
       <c r="E2" t="n">
-        <v>16.77803</v>
+        <v>16.53495</v>
       </c>
       <c r="F2" t="n">
-        <v>43.22007</v>
+        <v>42.34092</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05014</v>
+        <v>0.05166</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84584</v>
+        <v>1.84436</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.92903</v>
+        <v>16.63747</v>
       </c>
       <c r="D3" t="n">
-        <v>16.36416</v>
+        <v>16.34915</v>
       </c>
       <c r="E3" t="n">
-        <v>16.71364</v>
+        <v>16.52851</v>
       </c>
       <c r="F3" t="n">
-        <v>43.56253</v>
+        <v>42.48925</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05159</v>
+        <v>0.05077</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81312</v>
+        <v>1.81484</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.81871</v>
+        <v>16.91424</v>
       </c>
       <c r="D4" t="n">
-        <v>16.82425</v>
+        <v>16.83773</v>
       </c>
       <c r="E4" t="n">
-        <v>17.0235</v>
+        <v>16.85794</v>
       </c>
       <c r="F4" t="n">
-        <v>42.51044</v>
+        <v>42.88128</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05088</v>
+        <v>0.05082</v>
       </c>
       <c r="H4" t="n">
-        <v>1.87601</v>
+        <v>1.82517</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.90484</v>
+        <v>16.75525</v>
       </c>
       <c r="D6" t="n">
-        <v>16.06242</v>
+        <v>15.6499</v>
       </c>
       <c r="E6" t="n">
-        <v>16.5882</v>
+        <v>16.20579</v>
       </c>
       <c r="F6" t="n">
-        <v>21.31622</v>
+        <v>21.70676</v>
       </c>
       <c r="G6" t="n">
-        <v>35.56425</v>
+        <v>34.31559</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.00062</v>
+        <v>16.90478</v>
       </c>
       <c r="D7" t="n">
-        <v>16.09555</v>
+        <v>16.25099</v>
       </c>
       <c r="E7" t="n">
-        <v>16.50232</v>
+        <v>16.82582</v>
       </c>
       <c r="F7" t="n">
-        <v>22.21617</v>
+        <v>21.65375</v>
       </c>
       <c r="G7" t="n">
-        <v>34.07556</v>
+        <v>34.24514</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.10946</v>
+        <v>16.58541</v>
       </c>
       <c r="D8" t="n">
-        <v>16.08531</v>
+        <v>16.26644</v>
       </c>
       <c r="E8" t="n">
-        <v>16.59655</v>
+        <v>16.43238</v>
       </c>
       <c r="F8" t="n">
-        <v>21.95867</v>
+        <v>22.15451</v>
       </c>
       <c r="G8" t="n">
-        <v>34.34441</v>
+        <v>34.44054</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.61387</v>
+        <v>0.60798</v>
       </c>
       <c r="D10" t="n">
-        <v>1.12547</v>
+        <v>1.10283</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.60697</v>
+        <v>0.61524</v>
       </c>
       <c r="D11" t="n">
-        <v>1.12345</v>
+        <v>1.10865</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.61602</v>
+        <v>0.61439</v>
       </c>
       <c r="D12" t="n">
-        <v>1.12128</v>
+        <v>1.09801</v>
       </c>
     </row>
   </sheetData>
